--- a/backtest_runs/20260410_193731/by_symbol/SHNI/SHNI.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/SHNI/SHNI.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-5405.280000000005</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>94594.72</v>
@@ -633,7 +633,7 @@
         <v>-5292.669999999997</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>97635.19</v>
@@ -817,7 +817,7 @@
         <v>-6756.599999999996</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>101463.93</v>
@@ -863,7 +863,7 @@
         <v>-2364.809999999989</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>99099.12000000002</v>
@@ -909,7 +909,7 @@
         <v>-5405.280000000005</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>93693.84000000001</v>
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>98198.24000000002</v>
@@ -1277,7 +1277,7 @@
         <v>-10585.33999999999</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>92117.30000000003</v>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>92117.30000000003</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>92117.30000000003</v>
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>92117.30000000003</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>92117.30000000003</v>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>92117.30000000003</v>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>92117.30000000003</v>
